--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D3">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E3">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="G3">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>426</v>
